--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:26</t>
+    <t xml:space="preserve">2026-09-09 23:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:23</t>
+    <t xml:space="preserve">2026-09-17 14:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:18</t>
+    <t xml:space="preserve">2026-09-23 12:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_valparaiso.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:46</t>
+    <t xml:space="preserve">2026-10-01 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -174,7 +174,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre la mediana nacional (%)</t>
+    <t xml:space="preserve">% bajo 50% de la mediana</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -187,9 +187,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre mediana</t>
   </si>
 </sst>
 </file>
@@ -1301,7 +1298,7 @@
         <v>56</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:04</t>
+    <t xml:space="preserve">2026-10-02 11:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:19</t>
+    <t xml:space="preserve">2026-10-02 14:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:17</t>
+    <t xml:space="preserve">2026-10-04 09:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:21</t>
+    <t xml:space="preserve">2026-10-05 11:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
